--- a/SpreeCommerce_Automation/src/test/resources/spree_test_data.xlsx
+++ b/SpreeCommerce_Automation/src/test/resources/spree_test_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="8280"/>
   </bookViews>
   <sheets>
     <sheet name="spree_registration" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
     <t>Pal</t>
   </si>
   <si>
-    <t>arpitpal31@gmail.com</t>
+    <t>arpitpal101@gmail.com</t>
   </si>
   <si>
     <t>Test@123</t>
@@ -1340,9 +1340,6 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="arpitpal31@gmail.com" tooltip="mailto:arpitpal31@gmail.com"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1376,7 +1373,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="arpitpal31@gmail.com" tooltip="mailto:arpitpal31@gmail.com"/>
+    <hyperlink ref="A2" r:id="rId1" display="arpitpal101@gmail.com" tooltip="mailto:arpitpal101@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/SpreeCommerce_Automation/src/test/resources/spree_test_data.xlsx
+++ b/SpreeCommerce_Automation/src/test/resources/spree_test_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="spree_registration" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
   <si>
     <t>FirstName</t>
   </si>
@@ -53,7 +53,7 @@
     <t>Pal</t>
   </si>
   <si>
-    <t>arpitpal101@gmail.com</t>
+    <t>arpitpal174@gmail.com</t>
   </si>
   <si>
     <t>Test@123</t>
@@ -127,15 +127,15 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -610,12 +610,12 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -740,8 +740,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -750,6 +753,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -758,9 +764,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1306,40 +1309,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="6" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" display="arpitpal174@gmail.com" tooltip="mailto:arpitpal174@gmail.com"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1356,25 +1362,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="arpitpal101@gmail.com" tooltip="mailto:arpitpal101@gmail.com"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1390,12 +1393,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1408,73 +1411,80 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="12.8888888888889" customWidth="1"/>
-    <col min="2" max="2" width="9.44444444444444" customWidth="1"/>
-    <col min="3" max="4" width="11.1111111111111" customWidth="1"/>
-    <col min="5" max="5" width="11.6666666666667" customWidth="1"/>
-    <col min="6" max="7" width="10.2222222222222" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="1" max="1" width="21.3333333333333" customWidth="1"/>
+    <col min="2" max="2" width="12.8888888888889" customWidth="1"/>
+    <col min="3" max="3" width="9.44444444444444" customWidth="1"/>
+    <col min="4" max="5" width="11.1111111111111" customWidth="1"/>
+    <col min="6" max="6" width="11.6666666666667" customWidth="1"/>
+    <col min="7" max="8" width="10.2222222222222" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:10">
+      <c r="A2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="3">
+      <c r="I2" s="5">
         <v>10001</v>
       </c>
-      <c r="I2" s="4">
+      <c r="J2" s="6">
         <v>9876543210</v>
       </c>
     </row>

--- a/SpreeCommerce_Automation/src/test/resources/spree_test_data.xlsx
+++ b/SpreeCommerce_Automation/src/test/resources/spree_test_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="spree_registration" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
     <t>Pal</t>
   </si>
   <si>
-    <t>arpitpal174@gmail.com</t>
+    <t>arpitpal175@gmail.com</t>
   </si>
   <si>
     <t>Test@123</t>
@@ -1343,9 +1343,6 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="arpitpal174@gmail.com" tooltip="mailto:arpitpal174@gmail.com"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1378,6 +1375,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="arpitpal175@gmail.com"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1489,6 +1489,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="arpitpal175@gmail.com"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/SpreeCommerce_Automation/src/test/resources/spree_test_data.xlsx
+++ b/SpreeCommerce_Automation/src/test/resources/spree_test_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="spree_registration" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
     <t>Pal</t>
   </si>
   <si>
-    <t>arpitpal175@gmail.com</t>
+    <t>arpitpal176@gmail.com</t>
   </si>
   <si>
     <t>Test@123</t>
@@ -1343,6 +1343,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" display="arpitpal176@gmail.com"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1376,7 +1379,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="arpitpal175@gmail.com"/>
+    <hyperlink ref="A2" r:id="rId1" display="arpitpal176@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1490,7 +1493,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="arpitpal175@gmail.com"/>
+    <hyperlink ref="A2" r:id="rId1" display="arpitpal176@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
